--- a/site/leagues/proliga/2026_2027/xlsx/shot_packs/shot_pack_BCB.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/shot_packs/shot_pack_BCB.xlsx
@@ -684,8 +684,8 @@
   <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -982,12 +982,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
+          <t>BCB_A._GOMES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1175,8 +1175,8 @@
   <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -1681,12 +1681,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
+          <t>BCB_A._GOMES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2141,8 +2141,8 @@
   <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -2570,12 +2570,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
+          <t>BCB_A._GOMES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2813,8 +2813,8 @@
   <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -3072,12 +3072,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
+          <t>BCB_A._GOMES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3526,8 +3526,8 @@
   <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -3729,12 +3729,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
+          <t>BCB_A._GOMES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4192,8 +4192,8 @@
   <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -4645,12 +4645,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
+          <t>BCB_A._GOMES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5033,8 +5033,8 @@
   <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -5331,12 +5331,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
+          <t>BCB_A._GOMES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
